--- a/Test Code/UpgradeGenny/Upgrades.xlsx
+++ b/Test Code/UpgradeGenny/Upgrades.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\Test Code\UpgradeGenny\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4153CE-A6E7-4D92-A5E5-700969F467E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1908607-E4AE-4972-8ED8-2B57B44C9ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="1695" windowWidth="27435" windowHeight="19245" xr2:uid="{9F70EAB0-1489-41EB-8464-6B65151E08A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9F70EAB0-1489-41EB-8464-6B65151E08A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -90,15 +90,6 @@
   </si>
   <si>
     <t>This Ship may take a Cloaking Keel for +15 points, gaining Stealth and Cloak-2 (but only if it has no Engine Upgrade)</t>
-  </si>
-  <si>
-    <t>Daemon, Dragon, Devil, Nephilim, Samael, Bael, Faust, Raum</t>
-  </si>
-  <si>
-    <t>Cloaking Keel</t>
-  </si>
-  <si>
-    <t>Engine Upgrade</t>
   </si>
   <si>
     <t>This Ship may take an Engine Upgrade for +25 points increasing Thrust by 3” (but only if it has no Cloaking Keel)</t>
@@ -2148,6 +2139,27 @@
   </si>
   <si>
     <t>Light Cruiser, Cruiser, Heavy Cruiser</t>
+  </si>
+  <si>
+    <t>This Ship must take either a Cloaking Keel, gaining Stealth and Cloak-2, or an Engine Upgrade for +10 points, increasing Thrust by 3”.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nephilim, Samael, Bael, Faust</t>
+  </si>
+  <si>
+    <t>Daemon, Dragon, Devil</t>
+  </si>
+  <si>
+    <t>Keel Refit (Engine Upgrade)</t>
+  </si>
+  <si>
+    <t>Keel Refit (Cloaking Keel)</t>
+  </si>
+  <si>
+    <t>Keel Options (Cloaking Keel)</t>
+  </si>
+  <si>
+    <t>Keel Options (Engine Upgrade)</t>
   </si>
 </sst>
 </file>
@@ -2531,11 +2543,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8929AA1-D6BD-44CF-94F0-94B26B216493}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="70.42578125" customWidth="1"/>
+    <col min="2" max="2" width="112.7109375" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
     <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2610,13 +2622,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="D5">
         <v>15</v>
@@ -2627,13 +2639,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="D6">
         <v>25</v>
@@ -2642,450 +2654,484 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8">
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9">
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11">
         <v>18</v>
       </c>
-      <c r="E9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10">
-        <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>50</v>
+        <v>58</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D13">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14">
         <v>25</v>
       </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14">
-        <v>40</v>
-      </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D15">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D16">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18">
         <v>45</v>
       </c>
-      <c r="E16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17">
-        <v>40</v>
-      </c>
-      <c r="E17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
         <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>74</v>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D21">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D22">
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D24">
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D25">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D26">
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D28">
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>60</v>
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D29">
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D30">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D31">
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C32" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32">
+      <c r="C33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33">
+        <v>10</v>
+      </c>
+      <c r="E33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34">
         <v>6</v>
       </c>
-      <c r="E32" t="s">
-        <v>44</v>
+      <c r="E34" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E32" xr:uid="{D8929AA1-D6BD-44CF-94F0-94B26B216493}"/>
+  <autoFilter ref="A1:E34" xr:uid="{D8929AA1-D6BD-44CF-94F0-94B26B216493}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Test Code/UpgradeGenny/Upgrades.xlsx
+++ b/Test Code/UpgradeGenny/Upgrades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\Test Code\UpgradeGenny\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1908607-E4AE-4972-8ED8-2B57B44C9ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9ADE3D-A653-4185-973F-E0A47A1F9FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9F70EAB0-1489-41EB-8464-6B65151E08A5}"/>
+    <workbookView xWindow="1875" yWindow="810" windowWidth="33630" windowHeight="19245" xr2:uid="{9F70EAB0-1489-41EB-8464-6B65151E08A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
   <si>
     <t>Name</t>
   </si>
@@ -2160,6 +2160,18 @@
   </si>
   <si>
     <t>Keel Options (Engine Upgrade)</t>
+  </si>
+  <si>
+    <t>Drive Augmentation</t>
+  </si>
+  <si>
+    <t>This Ship may take a Drive Augmentation for +35 points, increasing its Thrust by 3”.</t>
+  </si>
+  <si>
+    <t>Diamond, Platinum, Gold, Silver, Bronze, Copper, Iron</t>
+  </si>
+  <si>
+    <t>Shaltari</t>
   </si>
 </sst>
 </file>
@@ -2543,7 +2555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8929AA1-D6BD-44CF-94F0-94B26B216493}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -3130,6 +3142,23 @@
         <v>41</v>
       </c>
     </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35">
+        <v>35</v>
+      </c>
+      <c r="E35" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E34" xr:uid="{D8929AA1-D6BD-44CF-94F0-94B26B216493}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Test Code/UpgradeGenny/Upgrades.xlsx
+++ b/Test Code/UpgradeGenny/Upgrades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\Test Code\UpgradeGenny\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9ADE3D-A653-4185-973F-E0A47A1F9FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24B9D0C-8658-4F7A-9D77-6EE23243CCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="810" windowWidth="33630" windowHeight="19245" xr2:uid="{9F70EAB0-1489-41EB-8464-6B65151E08A5}"/>
+    <workbookView xWindow="41130" yWindow="855" windowWidth="25260" windowHeight="15345" xr2:uid="{9F70EAB0-1489-41EB-8464-6B65151E08A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="93">
   <si>
     <t>Name</t>
   </si>
@@ -2172,6 +2172,78 @@
   </si>
   <si>
     <t>Shaltari</t>
+  </si>
+  <si>
+    <t>Mines</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Launch:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2
+Mine and Fighters &amp; Bombers use the same broadside component</t>
+    </r>
+  </si>
+  <si>
+    <t>Minelayer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Launch:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2
+This Ship has replaced it's Fighters &amp; Bombers with Mines fo +10 pts</t>
+    </r>
+  </si>
+  <si>
+    <t>Ikarus</t>
+  </si>
+  <si>
+    <t>PHR</t>
+  </si>
+  <si>
+    <t>Hydra</t>
+  </si>
+  <si>
+    <t>Basalt</t>
+  </si>
+  <si>
+    <t>Cavern</t>
+  </si>
+  <si>
+    <t>Bioficer</t>
   </si>
 </sst>
 </file>
@@ -2555,7 +2627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8929AA1-D6BD-44CF-94F0-94B26B216493}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
@@ -3159,6 +3231,91 @@
         <v>82</v>
       </c>
     </row>
+    <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36">
+        <v>35</v>
+      </c>
+      <c r="E36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39">
+        <v>10</v>
+      </c>
+      <c r="E39" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E34" xr:uid="{D8929AA1-D6BD-44CF-94F0-94B26B216493}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
